--- a/DATA/MODELADO/Bitacoras/Exp04/bitacora_maestra_experimentos.xlsx
+++ b/DATA/MODELADO/Bitacoras/Exp04/bitacora_maestra_experimentos.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AI3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46234.06075361478</v>
+        <v>46234.06075361111</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -726,6 +726,113 @@
       </c>
       <c r="AI2" t="n">
         <v>10.65025329589844</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Exp04</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>46234.10205650901</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Gestión Hídrica</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RobustScaler</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>516</v>
+      </c>
+      <c r="J3" t="n">
+        <v>361</v>
+      </c>
+      <c r="K3" t="n">
+        <v>77</v>
+      </c>
+      <c r="L3" t="n">
+        <v>78</v>
+      </c>
+      <c r="M3" t="n">
+        <v>32</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P3" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>100</v>
+      </c>
+      <c r="R3" t="n">
+        <v>100</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.00463638361543417</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.03598886355757713</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.07414160668849945</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.04165492206811905</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1639291346073151</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.06809099763631821</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.1897073090076447</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.2453693002462387</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.2722895741462708</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
+        <v>24.39480328559875</v>
       </c>
     </row>
   </sheetData>
